--- a/electron-app/斯诺德跑团/冒险者角色档案_空白模板.xlsx
+++ b/electron-app/斯诺德跑团/冒险者角色档案_空白模板.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="154">
   <si>
     <t>基础信息</t>
   </si>
@@ -487,6 +487,9 @@
   </si>
   <si>
     <t>子职业（）</t>
+  </si>
+  <si>
+    <t>图纸(专业槽位)</t>
   </si>
 </sst>
 </file>
@@ -1550,7 +1553,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1803,7 +1806,13 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4626,10 +4635,10 @@
       <c r="G123" s="61"/>
       <c r="H123" s="63"/>
       <c r="I123" s="63"/>
-      <c r="J123" s="60"/>
-      <c r="K123" s="84"/>
-      <c r="L123" s="84"/>
-      <c r="M123" s="61"/>
+      <c r="J123" s="84"/>
+      <c r="K123" s="85"/>
+      <c r="L123" s="85"/>
+      <c r="M123" s="86"/>
       <c r="O123" s="15"/>
       <c r="P123" s="16"/>
       <c r="Q123" s="15"/>
@@ -4645,10 +4654,10 @@
       <c r="G124" s="61"/>
       <c r="H124" s="63"/>
       <c r="I124" s="63"/>
-      <c r="J124" s="60"/>
-      <c r="K124" s="84"/>
-      <c r="L124" s="84"/>
-      <c r="M124" s="61"/>
+      <c r="J124" s="84"/>
+      <c r="K124" s="85"/>
+      <c r="L124" s="85"/>
+      <c r="M124" s="86"/>
       <c r="O124" s="15"/>
       <c r="P124" s="16"/>
       <c r="Q124" s="15"/>
@@ -4664,10 +4673,10 @@
       <c r="G125" s="61"/>
       <c r="H125" s="63"/>
       <c r="I125" s="63"/>
-      <c r="J125" s="60"/>
-      <c r="K125" s="84"/>
-      <c r="L125" s="84"/>
-      <c r="M125" s="61"/>
+      <c r="J125" s="84"/>
+      <c r="K125" s="85"/>
+      <c r="L125" s="85"/>
+      <c r="M125" s="86"/>
       <c r="O125" s="15"/>
       <c r="P125" s="16"/>
       <c r="Q125" s="15"/>
@@ -4683,10 +4692,10 @@
       <c r="G126" s="61"/>
       <c r="H126" s="63"/>
       <c r="I126" s="63"/>
-      <c r="J126" s="60"/>
-      <c r="K126" s="84"/>
-      <c r="L126" s="84"/>
-      <c r="M126" s="61"/>
+      <c r="J126" s="84"/>
+      <c r="K126" s="85"/>
+      <c r="L126" s="85"/>
+      <c r="M126" s="86"/>
       <c r="O126" s="15"/>
       <c r="P126" s="16"/>
       <c r="Q126" s="15"/>
@@ -4702,10 +4711,10 @@
       <c r="G127" s="61"/>
       <c r="H127" s="63"/>
       <c r="I127" s="63"/>
-      <c r="J127" s="60"/>
-      <c r="K127" s="84"/>
-      <c r="L127" s="84"/>
-      <c r="M127" s="61"/>
+      <c r="J127" s="84"/>
+      <c r="K127" s="85"/>
+      <c r="L127" s="85"/>
+      <c r="M127" s="86"/>
     </row>
     <row r="128" s="1" customFormat="1" customHeight="1" spans="2:19">
       <c r="B128" s="15"/>
@@ -4716,10 +4725,10 @@
       <c r="G128" s="61"/>
       <c r="H128" s="63"/>
       <c r="I128" s="63"/>
-      <c r="J128" s="60"/>
-      <c r="K128" s="84"/>
-      <c r="L128" s="84"/>
-      <c r="M128" s="61"/>
+      <c r="J128" s="84"/>
+      <c r="K128" s="85"/>
+      <c r="L128" s="85"/>
+      <c r="M128" s="86"/>
       <c r="O128" s="6" t="s">
         <v>146</v>
       </c>
@@ -4737,10 +4746,10 @@
       <c r="G129" s="61"/>
       <c r="H129" s="63"/>
       <c r="I129" s="63"/>
-      <c r="J129" s="60"/>
-      <c r="K129" s="84"/>
-      <c r="L129" s="84"/>
-      <c r="M129" s="61"/>
+      <c r="J129" s="84"/>
+      <c r="K129" s="85"/>
+      <c r="L129" s="85"/>
+      <c r="M129" s="86"/>
       <c r="O129" s="15"/>
       <c r="P129" s="16"/>
       <c r="Q129" s="15"/>
@@ -4756,10 +4765,10 @@
       <c r="G130" s="61"/>
       <c r="H130" s="63"/>
       <c r="I130" s="63"/>
-      <c r="J130" s="60"/>
-      <c r="K130" s="84"/>
-      <c r="L130" s="84"/>
-      <c r="M130" s="61"/>
+      <c r="J130" s="84"/>
+      <c r="K130" s="85"/>
+      <c r="L130" s="85"/>
+      <c r="M130" s="86"/>
       <c r="O130" s="15"/>
       <c r="P130" s="16"/>
       <c r="Q130" s="15"/>
@@ -4775,10 +4784,10 @@
       <c r="G131" s="61"/>
       <c r="H131" s="63"/>
       <c r="I131" s="63"/>
-      <c r="J131" s="60"/>
-      <c r="K131" s="84"/>
-      <c r="L131" s="84"/>
-      <c r="M131" s="61"/>
+      <c r="J131" s="84"/>
+      <c r="K131" s="85"/>
+      <c r="L131" s="85"/>
+      <c r="M131" s="86"/>
       <c r="O131" s="15"/>
       <c r="P131" s="16"/>
       <c r="Q131" s="15"/>
@@ -4794,10 +4803,10 @@
       <c r="G132" s="61"/>
       <c r="H132" s="63"/>
       <c r="I132" s="63"/>
-      <c r="J132" s="60"/>
-      <c r="K132" s="84"/>
-      <c r="L132" s="84"/>
-      <c r="M132" s="61"/>
+      <c r="J132" s="84"/>
+      <c r="K132" s="85"/>
+      <c r="L132" s="85"/>
+      <c r="M132" s="86"/>
       <c r="O132" s="15"/>
       <c r="P132" s="16"/>
       <c r="Q132" s="15"/>
@@ -4813,10 +4822,10 @@
       <c r="G133" s="61"/>
       <c r="H133" s="63"/>
       <c r="I133" s="63"/>
-      <c r="J133" s="60"/>
-      <c r="K133" s="84"/>
-      <c r="L133" s="84"/>
-      <c r="M133" s="61"/>
+      <c r="J133" s="84"/>
+      <c r="K133" s="85"/>
+      <c r="L133" s="85"/>
+      <c r="M133" s="86"/>
       <c r="O133" s="15"/>
       <c r="P133" s="16"/>
       <c r="Q133" s="15"/>
@@ -4832,10 +4841,10 @@
       <c r="G134" s="61"/>
       <c r="H134" s="63"/>
       <c r="I134" s="63"/>
-      <c r="J134" s="60"/>
-      <c r="K134" s="84"/>
-      <c r="L134" s="84"/>
-      <c r="M134" s="61"/>
+      <c r="J134" s="84"/>
+      <c r="K134" s="85"/>
+      <c r="L134" s="85"/>
+      <c r="M134" s="86"/>
     </row>
     <row r="135" s="1" customFormat="1" customHeight="1" spans="2:19">
       <c r="B135" s="15"/>
@@ -4846,10 +4855,10 @@
       <c r="G135" s="61"/>
       <c r="H135" s="63"/>
       <c r="I135" s="63"/>
-      <c r="J135" s="60"/>
-      <c r="K135" s="84"/>
-      <c r="L135" s="84"/>
-      <c r="M135" s="61"/>
+      <c r="J135" s="84"/>
+      <c r="K135" s="85"/>
+      <c r="L135" s="85"/>
+      <c r="M135" s="86"/>
       <c r="O135" s="6" t="s">
         <v>147</v>
       </c>
@@ -4867,10 +4876,10 @@
       <c r="G136" s="61"/>
       <c r="H136" s="63"/>
       <c r="I136" s="63"/>
-      <c r="J136" s="60"/>
-      <c r="K136" s="84"/>
-      <c r="L136" s="84"/>
-      <c r="M136" s="61"/>
+      <c r="J136" s="84"/>
+      <c r="K136" s="85"/>
+      <c r="L136" s="85"/>
+      <c r="M136" s="86"/>
       <c r="O136" s="15"/>
       <c r="P136" s="16"/>
       <c r="Q136" s="15"/>
@@ -4886,10 +4895,10 @@
       <c r="G137" s="61"/>
       <c r="H137" s="63"/>
       <c r="I137" s="63"/>
-      <c r="J137" s="60"/>
-      <c r="K137" s="84"/>
-      <c r="L137" s="84"/>
-      <c r="M137" s="61"/>
+      <c r="J137" s="84"/>
+      <c r="K137" s="85"/>
+      <c r="L137" s="85"/>
+      <c r="M137" s="86"/>
       <c r="O137" s="15"/>
       <c r="P137" s="16"/>
       <c r="Q137" s="15"/>
@@ -4905,10 +4914,10 @@
       <c r="G138" s="61"/>
       <c r="H138" s="63"/>
       <c r="I138" s="63"/>
-      <c r="J138" s="60"/>
-      <c r="K138" s="84"/>
-      <c r="L138" s="84"/>
-      <c r="M138" s="61"/>
+      <c r="J138" s="84"/>
+      <c r="K138" s="85"/>
+      <c r="L138" s="85"/>
+      <c r="M138" s="86"/>
       <c r="O138" s="15"/>
       <c r="P138" s="16"/>
       <c r="Q138" s="15"/>
@@ -4924,10 +4933,10 @@
       <c r="G139" s="61"/>
       <c r="H139" s="63"/>
       <c r="I139" s="63"/>
-      <c r="J139" s="60"/>
-      <c r="K139" s="84"/>
-      <c r="L139" s="84"/>
-      <c r="M139" s="61"/>
+      <c r="J139" s="84"/>
+      <c r="K139" s="85"/>
+      <c r="L139" s="85"/>
+      <c r="M139" s="86"/>
       <c r="O139" s="15"/>
       <c r="P139" s="16"/>
       <c r="Q139" s="15"/>
@@ -4943,10 +4952,10 @@
       <c r="G140" s="61"/>
       <c r="H140" s="63"/>
       <c r="I140" s="63"/>
-      <c r="J140" s="60"/>
-      <c r="K140" s="84"/>
-      <c r="L140" s="84"/>
-      <c r="M140" s="61"/>
+      <c r="J140" s="84"/>
+      <c r="K140" s="85"/>
+      <c r="L140" s="85"/>
+      <c r="M140" s="86"/>
       <c r="O140" s="15"/>
       <c r="P140" s="16"/>
       <c r="Q140" s="15"/>
@@ -4962,10 +4971,10 @@
       <c r="G141" s="61"/>
       <c r="H141" s="63"/>
       <c r="I141" s="63"/>
-      <c r="J141" s="60"/>
-      <c r="K141" s="84"/>
-      <c r="L141" s="84"/>
-      <c r="M141" s="61"/>
+      <c r="J141" s="84"/>
+      <c r="K141" s="85"/>
+      <c r="L141" s="85"/>
+      <c r="M141" s="86"/>
     </row>
     <row r="142" s="1" customFormat="1" customHeight="1" spans="2:19">
       <c r="B142" s="15"/>
@@ -4976,10 +4985,10 @@
       <c r="G142" s="61"/>
       <c r="H142" s="63"/>
       <c r="I142" s="63"/>
-      <c r="J142" s="60"/>
-      <c r="K142" s="84"/>
-      <c r="L142" s="84"/>
-      <c r="M142" s="61"/>
+      <c r="J142" s="84"/>
+      <c r="K142" s="85"/>
+      <c r="L142" s="85"/>
+      <c r="M142" s="86"/>
       <c r="O142" s="6" t="s">
         <v>148</v>
       </c>
@@ -4997,10 +5006,10 @@
       <c r="G143" s="61"/>
       <c r="H143" s="63"/>
       <c r="I143" s="63"/>
-      <c r="J143" s="60"/>
-      <c r="K143" s="84"/>
-      <c r="L143" s="84"/>
-      <c r="M143" s="61"/>
+      <c r="J143" s="84"/>
+      <c r="K143" s="85"/>
+      <c r="L143" s="85"/>
+      <c r="M143" s="86"/>
       <c r="O143" s="15"/>
       <c r="P143" s="16"/>
       <c r="Q143" s="15"/>
@@ -5016,10 +5025,10 @@
       <c r="G144" s="61"/>
       <c r="H144" s="63"/>
       <c r="I144" s="63"/>
-      <c r="J144" s="60"/>
-      <c r="K144" s="84"/>
-      <c r="L144" s="84"/>
-      <c r="M144" s="61"/>
+      <c r="J144" s="84"/>
+      <c r="K144" s="85"/>
+      <c r="L144" s="85"/>
+      <c r="M144" s="86"/>
       <c r="O144" s="15"/>
       <c r="P144" s="16"/>
       <c r="Q144" s="15"/>
@@ -5035,10 +5044,10 @@
       <c r="G145" s="61"/>
       <c r="H145" s="63"/>
       <c r="I145" s="63"/>
-      <c r="J145" s="60"/>
-      <c r="K145" s="84"/>
-      <c r="L145" s="84"/>
-      <c r="M145" s="61"/>
+      <c r="J145" s="84"/>
+      <c r="K145" s="85"/>
+      <c r="L145" s="85"/>
+      <c r="M145" s="86"/>
       <c r="O145" s="15"/>
       <c r="P145" s="16"/>
       <c r="Q145" s="15"/>
@@ -5054,10 +5063,10 @@
       <c r="G146" s="61"/>
       <c r="H146" s="63"/>
       <c r="I146" s="63"/>
-      <c r="J146" s="60"/>
-      <c r="K146" s="84"/>
-      <c r="L146" s="84"/>
-      <c r="M146" s="61"/>
+      <c r="J146" s="84"/>
+      <c r="K146" s="85"/>
+      <c r="L146" s="85"/>
+      <c r="M146" s="86"/>
       <c r="O146" s="15"/>
       <c r="P146" s="16"/>
       <c r="Q146" s="15"/>
@@ -5073,10 +5082,10 @@
       <c r="G147" s="61"/>
       <c r="H147" s="63"/>
       <c r="I147" s="63"/>
-      <c r="J147" s="60"/>
-      <c r="K147" s="84"/>
-      <c r="L147" s="84"/>
-      <c r="M147" s="61"/>
+      <c r="J147" s="84"/>
+      <c r="K147" s="85"/>
+      <c r="L147" s="85"/>
+      <c r="M147" s="86"/>
       <c r="O147" s="15"/>
       <c r="P147" s="16"/>
       <c r="Q147" s="15"/>
@@ -5092,10 +5101,10 @@
       <c r="G148" s="61"/>
       <c r="H148" s="63"/>
       <c r="I148" s="63"/>
-      <c r="J148" s="60"/>
-      <c r="K148" s="84"/>
-      <c r="L148" s="84"/>
-      <c r="M148" s="61"/>
+      <c r="J148" s="84"/>
+      <c r="K148" s="85"/>
+      <c r="L148" s="85"/>
+      <c r="M148" s="86"/>
     </row>
     <row r="149" customHeight="1" spans="2:19">
       <c r="B149" s="15"/>
@@ -5106,10 +5115,10 @@
       <c r="G149" s="61"/>
       <c r="H149" s="63"/>
       <c r="I149" s="63"/>
-      <c r="J149" s="60"/>
-      <c r="K149" s="84"/>
-      <c r="L149" s="84"/>
-      <c r="M149" s="61"/>
+      <c r="J149" s="84"/>
+      <c r="K149" s="85"/>
+      <c r="L149" s="85"/>
+      <c r="M149" s="86"/>
       <c r="O149" s="6" t="s">
         <v>149</v>
       </c>
@@ -5127,10 +5136,10 @@
       <c r="G150" s="61"/>
       <c r="H150" s="63"/>
       <c r="I150" s="63"/>
-      <c r="J150" s="60"/>
-      <c r="K150" s="84"/>
-      <c r="L150" s="84"/>
-      <c r="M150" s="61"/>
+      <c r="J150" s="84"/>
+      <c r="K150" s="85"/>
+      <c r="L150" s="85"/>
+      <c r="M150" s="86"/>
       <c r="O150" s="15"/>
       <c r="P150" s="16"/>
       <c r="Q150" s="15"/>
@@ -5146,10 +5155,10 @@
       <c r="G151" s="61"/>
       <c r="H151" s="63"/>
       <c r="I151" s="63"/>
-      <c r="J151" s="60"/>
-      <c r="K151" s="84"/>
-      <c r="L151" s="84"/>
-      <c r="M151" s="61"/>
+      <c r="J151" s="84"/>
+      <c r="K151" s="85"/>
+      <c r="L151" s="85"/>
+      <c r="M151" s="86"/>
       <c r="O151" s="15"/>
       <c r="P151" s="16"/>
       <c r="Q151" s="15"/>
@@ -5165,10 +5174,10 @@
       <c r="G152" s="61"/>
       <c r="H152" s="63"/>
       <c r="I152" s="63"/>
-      <c r="J152" s="60"/>
-      <c r="K152" s="84"/>
-      <c r="L152" s="84"/>
-      <c r="M152" s="61"/>
+      <c r="J152" s="84"/>
+      <c r="K152" s="85"/>
+      <c r="L152" s="85"/>
+      <c r="M152" s="86"/>
       <c r="O152" s="15"/>
       <c r="P152" s="16"/>
       <c r="Q152" s="15"/>
@@ -5184,10 +5193,10 @@
       <c r="G153" s="61"/>
       <c r="H153" s="63"/>
       <c r="I153" s="63"/>
-      <c r="J153" s="60"/>
-      <c r="K153" s="84"/>
-      <c r="L153" s="84"/>
-      <c r="M153" s="61"/>
+      <c r="J153" s="84"/>
+      <c r="K153" s="85"/>
+      <c r="L153" s="85"/>
+      <c r="M153" s="86"/>
       <c r="O153" s="15"/>
       <c r="P153" s="16"/>
       <c r="Q153" s="15"/>
@@ -5203,10 +5212,10 @@
       <c r="G154" s="61"/>
       <c r="H154" s="63"/>
       <c r="I154" s="63"/>
-      <c r="J154" s="60"/>
-      <c r="K154" s="84"/>
-      <c r="L154" s="84"/>
-      <c r="M154" s="61"/>
+      <c r="J154" s="84"/>
+      <c r="K154" s="85"/>
+      <c r="L154" s="85"/>
+      <c r="M154" s="86"/>
       <c r="O154" s="15"/>
       <c r="P154" s="16"/>
       <c r="Q154" s="15"/>
@@ -5222,10 +5231,10 @@
       <c r="G155" s="61"/>
       <c r="H155" s="63"/>
       <c r="I155" s="63"/>
-      <c r="J155" s="60"/>
-      <c r="K155" s="84"/>
-      <c r="L155" s="84"/>
-      <c r="M155" s="61"/>
+      <c r="J155" s="84"/>
+      <c r="K155" s="85"/>
+      <c r="L155" s="85"/>
+      <c r="M155" s="86"/>
     </row>
     <row r="156" customHeight="1" spans="2:19">
       <c r="B156" s="15"/>
@@ -5236,10 +5245,10 @@
       <c r="G156" s="61"/>
       <c r="H156" s="63"/>
       <c r="I156" s="63"/>
-      <c r="J156" s="60"/>
-      <c r="K156" s="84"/>
-      <c r="L156" s="84"/>
-      <c r="M156" s="61"/>
+      <c r="J156" s="84"/>
+      <c r="K156" s="85"/>
+      <c r="L156" s="85"/>
+      <c r="M156" s="86"/>
       <c r="O156" s="6" t="s">
         <v>150</v>
       </c>
@@ -5257,10 +5266,10 @@
       <c r="G157" s="61"/>
       <c r="H157" s="63"/>
       <c r="I157" s="63"/>
-      <c r="J157" s="60"/>
-      <c r="K157" s="84"/>
-      <c r="L157" s="84"/>
-      <c r="M157" s="61"/>
+      <c r="J157" s="84"/>
+      <c r="K157" s="85"/>
+      <c r="L157" s="85"/>
+      <c r="M157" s="86"/>
       <c r="O157" s="15"/>
       <c r="P157" s="16"/>
       <c r="Q157" s="15"/>
@@ -5276,10 +5285,10 @@
       <c r="G158" s="61"/>
       <c r="H158" s="63"/>
       <c r="I158" s="63"/>
-      <c r="J158" s="60"/>
-      <c r="K158" s="84"/>
-      <c r="L158" s="84"/>
-      <c r="M158" s="61"/>
+      <c r="J158" s="84"/>
+      <c r="K158" s="85"/>
+      <c r="L158" s="85"/>
+      <c r="M158" s="86"/>
       <c r="O158" s="15"/>
       <c r="P158" s="16"/>
       <c r="Q158" s="15"/>
@@ -5295,10 +5304,10 @@
       <c r="G159" s="61"/>
       <c r="H159" s="63"/>
       <c r="I159" s="63"/>
-      <c r="J159" s="60"/>
-      <c r="K159" s="84"/>
-      <c r="L159" s="84"/>
-      <c r="M159" s="61"/>
+      <c r="J159" s="84"/>
+      <c r="K159" s="85"/>
+      <c r="L159" s="85"/>
+      <c r="M159" s="86"/>
       <c r="O159" s="15"/>
       <c r="P159" s="16"/>
       <c r="Q159" s="15"/>
@@ -5314,10 +5323,10 @@
       <c r="G160" s="61"/>
       <c r="H160" s="63"/>
       <c r="I160" s="63"/>
-      <c r="J160" s="60"/>
-      <c r="K160" s="84"/>
-      <c r="L160" s="84"/>
-      <c r="M160" s="61"/>
+      <c r="J160" s="84"/>
+      <c r="K160" s="85"/>
+      <c r="L160" s="85"/>
+      <c r="M160" s="86"/>
       <c r="O160" s="15"/>
       <c r="P160" s="16"/>
       <c r="Q160" s="15"/>
@@ -5333,10 +5342,10 @@
       <c r="G161" s="61"/>
       <c r="H161" s="63"/>
       <c r="I161" s="63"/>
-      <c r="J161" s="60"/>
-      <c r="K161" s="84"/>
-      <c r="L161" s="84"/>
-      <c r="M161" s="61"/>
+      <c r="J161" s="84"/>
+      <c r="K161" s="85"/>
+      <c r="L161" s="85"/>
+      <c r="M161" s="86"/>
       <c r="O161" s="15"/>
       <c r="P161" s="16"/>
       <c r="Q161" s="15"/>
@@ -5352,10 +5361,10 @@
       <c r="G162" s="61"/>
       <c r="H162" s="63"/>
       <c r="I162" s="63"/>
-      <c r="J162" s="60"/>
-      <c r="K162" s="84"/>
-      <c r="L162" s="84"/>
-      <c r="M162" s="61"/>
+      <c r="J162" s="84"/>
+      <c r="K162" s="85"/>
+      <c r="L162" s="85"/>
+      <c r="M162" s="86"/>
     </row>
     <row r="163" customHeight="1" spans="2:19">
       <c r="O163" s="6" t="s">
@@ -5443,10 +5452,10 @@
       <c r="G168" s="61"/>
       <c r="H168" s="63"/>
       <c r="I168" s="63"/>
-      <c r="J168" s="60"/>
-      <c r="K168" s="84"/>
-      <c r="L168" s="84"/>
-      <c r="M168" s="61"/>
+      <c r="J168" s="84"/>
+      <c r="K168" s="85"/>
+      <c r="L168" s="85"/>
+      <c r="M168" s="86"/>
       <c r="O168" s="15"/>
       <c r="P168" s="16"/>
       <c r="Q168" s="15"/>
@@ -5462,10 +5471,10 @@
       <c r="G169" s="61"/>
       <c r="H169" s="63"/>
       <c r="I169" s="63"/>
-      <c r="J169" s="60"/>
-      <c r="K169" s="84"/>
-      <c r="L169" s="84"/>
-      <c r="M169" s="61"/>
+      <c r="J169" s="84"/>
+      <c r="K169" s="85"/>
+      <c r="L169" s="85"/>
+      <c r="M169" s="86"/>
     </row>
     <row r="170" customHeight="1" spans="2:19">
       <c r="B170" s="15"/>
@@ -5476,10 +5485,10 @@
       <c r="G170" s="61"/>
       <c r="H170" s="63"/>
       <c r="I170" s="63"/>
-      <c r="J170" s="60"/>
-      <c r="K170" s="84"/>
-      <c r="L170" s="84"/>
-      <c r="M170" s="61"/>
+      <c r="J170" s="84"/>
+      <c r="K170" s="85"/>
+      <c r="L170" s="85"/>
+      <c r="M170" s="86"/>
     </row>
     <row r="171" customHeight="1" spans="2:19">
       <c r="B171" s="15"/>
@@ -5490,10 +5499,10 @@
       <c r="G171" s="61"/>
       <c r="H171" s="63"/>
       <c r="I171" s="63"/>
-      <c r="J171" s="60"/>
-      <c r="K171" s="84"/>
-      <c r="L171" s="84"/>
-      <c r="M171" s="61"/>
+      <c r="J171" s="84"/>
+      <c r="K171" s="85"/>
+      <c r="L171" s="85"/>
+      <c r="M171" s="86"/>
     </row>
     <row r="172" customHeight="1" spans="2:19">
       <c r="B172" s="15"/>
@@ -5504,10 +5513,17 @@
       <c r="G172" s="61"/>
       <c r="H172" s="63"/>
       <c r="I172" s="63"/>
-      <c r="J172" s="60"/>
-      <c r="K172" s="84"/>
-      <c r="L172" s="84"/>
-      <c r="M172" s="61"/>
+      <c r="J172" s="84"/>
+      <c r="K172" s="85"/>
+      <c r="L172" s="85"/>
+      <c r="M172" s="86"/>
+      <c r="O172" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="P172" s="7"/>
+      <c r="Q172" s="7"/>
+      <c r="R172" s="7"/>
+      <c r="S172" s="8"/>
     </row>
     <row r="173" customHeight="1" spans="2:19">
       <c r="B173" s="15"/>
@@ -5518,10 +5534,15 @@
       <c r="G173" s="61"/>
       <c r="H173" s="63"/>
       <c r="I173" s="63"/>
-      <c r="J173" s="60"/>
-      <c r="K173" s="84"/>
-      <c r="L173" s="84"/>
-      <c r="M173" s="61"/>
+      <c r="J173" s="84"/>
+      <c r="K173" s="85"/>
+      <c r="L173" s="85"/>
+      <c r="M173" s="86"/>
+      <c r="O173" s="15"/>
+      <c r="P173" s="16"/>
+      <c r="Q173" s="15"/>
+      <c r="R173" s="16"/>
+      <c r="S173" s="83"/>
     </row>
     <row r="174" customHeight="1" spans="2:19">
       <c r="B174" s="15"/>
@@ -5532,10 +5553,15 @@
       <c r="G174" s="61"/>
       <c r="H174" s="63"/>
       <c r="I174" s="63"/>
-      <c r="J174" s="60"/>
-      <c r="K174" s="84"/>
-      <c r="L174" s="84"/>
-      <c r="M174" s="61"/>
+      <c r="J174" s="84"/>
+      <c r="K174" s="85"/>
+      <c r="L174" s="85"/>
+      <c r="M174" s="86"/>
+      <c r="O174" s="15"/>
+      <c r="P174" s="16"/>
+      <c r="Q174" s="15"/>
+      <c r="R174" s="16"/>
+      <c r="S174" s="83"/>
     </row>
     <row r="175" customHeight="1" spans="2:19">
       <c r="B175" s="15"/>
@@ -5546,10 +5572,15 @@
       <c r="G175" s="61"/>
       <c r="H175" s="63"/>
       <c r="I175" s="63"/>
-      <c r="J175" s="60"/>
-      <c r="K175" s="84"/>
-      <c r="L175" s="84"/>
-      <c r="M175" s="61"/>
+      <c r="J175" s="84"/>
+      <c r="K175" s="85"/>
+      <c r="L175" s="85"/>
+      <c r="M175" s="86"/>
+      <c r="O175" s="15"/>
+      <c r="P175" s="16"/>
+      <c r="Q175" s="15"/>
+      <c r="R175" s="16"/>
+      <c r="S175" s="83"/>
     </row>
     <row r="176" customHeight="1" spans="2:19">
       <c r="B176" s="15"/>
@@ -5560,12 +5591,17 @@
       <c r="G176" s="61"/>
       <c r="H176" s="63"/>
       <c r="I176" s="63"/>
-      <c r="J176" s="60"/>
-      <c r="K176" s="84"/>
-      <c r="L176" s="84"/>
-      <c r="M176" s="61"/>
-    </row>
-    <row r="177" customHeight="1" spans="2:13">
+      <c r="J176" s="84"/>
+      <c r="K176" s="85"/>
+      <c r="L176" s="85"/>
+      <c r="M176" s="86"/>
+      <c r="O176" s="15"/>
+      <c r="P176" s="16"/>
+      <c r="Q176" s="15"/>
+      <c r="R176" s="16"/>
+      <c r="S176" s="83"/>
+    </row>
+    <row r="177" customHeight="1" spans="2:19">
       <c r="B177" s="15"/>
       <c r="C177" s="16"/>
       <c r="D177" s="63"/>
@@ -5574,12 +5610,17 @@
       <c r="G177" s="61"/>
       <c r="H177" s="63"/>
       <c r="I177" s="63"/>
-      <c r="J177" s="60"/>
-      <c r="K177" s="84"/>
-      <c r="L177" s="84"/>
-      <c r="M177" s="61"/>
-    </row>
-    <row r="178" customHeight="1" spans="2:13">
+      <c r="J177" s="84"/>
+      <c r="K177" s="85"/>
+      <c r="L177" s="85"/>
+      <c r="M177" s="86"/>
+      <c r="O177" s="15"/>
+      <c r="P177" s="16"/>
+      <c r="Q177" s="15"/>
+      <c r="R177" s="16"/>
+      <c r="S177" s="83"/>
+    </row>
+    <row r="178" customHeight="1" spans="2:19">
       <c r="B178" s="15"/>
       <c r="C178" s="16"/>
       <c r="D178" s="63"/>
@@ -5588,12 +5629,17 @@
       <c r="G178" s="61"/>
       <c r="H178" s="63"/>
       <c r="I178" s="63"/>
-      <c r="J178" s="60"/>
-      <c r="K178" s="84"/>
-      <c r="L178" s="84"/>
-      <c r="M178" s="61"/>
-    </row>
-    <row r="179" customHeight="1" spans="2:13">
+      <c r="J178" s="84"/>
+      <c r="K178" s="85"/>
+      <c r="L178" s="85"/>
+      <c r="M178" s="86"/>
+      <c r="O178" s="15"/>
+      <c r="P178" s="16"/>
+      <c r="Q178" s="15"/>
+      <c r="R178" s="16"/>
+      <c r="S178" s="83"/>
+    </row>
+    <row r="179" customHeight="1" spans="2:19">
       <c r="B179" s="15"/>
       <c r="C179" s="16"/>
       <c r="D179" s="63"/>
@@ -5602,12 +5648,17 @@
       <c r="G179" s="61"/>
       <c r="H179" s="63"/>
       <c r="I179" s="63"/>
-      <c r="J179" s="60"/>
-      <c r="K179" s="84"/>
-      <c r="L179" s="84"/>
-      <c r="M179" s="61"/>
-    </row>
-    <row r="180" customHeight="1" spans="2:13">
+      <c r="J179" s="84"/>
+      <c r="K179" s="85"/>
+      <c r="L179" s="85"/>
+      <c r="M179" s="86"/>
+      <c r="O179" s="15"/>
+      <c r="P179" s="16"/>
+      <c r="Q179" s="15"/>
+      <c r="R179" s="16"/>
+      <c r="S179" s="83"/>
+    </row>
+    <row r="180" customHeight="1" spans="2:19">
       <c r="B180" s="15"/>
       <c r="C180" s="16"/>
       <c r="D180" s="63"/>
@@ -5616,12 +5667,17 @@
       <c r="G180" s="61"/>
       <c r="H180" s="63"/>
       <c r="I180" s="63"/>
-      <c r="J180" s="60"/>
-      <c r="K180" s="84"/>
-      <c r="L180" s="84"/>
-      <c r="M180" s="61"/>
-    </row>
-    <row r="181" customHeight="1" spans="2:13">
+      <c r="J180" s="84"/>
+      <c r="K180" s="85"/>
+      <c r="L180" s="85"/>
+      <c r="M180" s="86"/>
+      <c r="O180" s="15"/>
+      <c r="P180" s="16"/>
+      <c r="Q180" s="15"/>
+      <c r="R180" s="16"/>
+      <c r="S180" s="83"/>
+    </row>
+    <row r="181" customHeight="1" spans="2:19">
       <c r="B181" s="15"/>
       <c r="C181" s="16"/>
       <c r="D181" s="63"/>
@@ -5630,12 +5686,17 @@
       <c r="G181" s="61"/>
       <c r="H181" s="63"/>
       <c r="I181" s="63"/>
-      <c r="J181" s="60"/>
-      <c r="K181" s="84"/>
-      <c r="L181" s="84"/>
-      <c r="M181" s="61"/>
-    </row>
-    <row r="182" customHeight="1" spans="2:13">
+      <c r="J181" s="84"/>
+      <c r="K181" s="85"/>
+      <c r="L181" s="85"/>
+      <c r="M181" s="86"/>
+      <c r="O181" s="15"/>
+      <c r="P181" s="16"/>
+      <c r="Q181" s="15"/>
+      <c r="R181" s="16"/>
+      <c r="S181" s="83"/>
+    </row>
+    <row r="182" customHeight="1" spans="2:19">
       <c r="B182" s="15"/>
       <c r="C182" s="16"/>
       <c r="D182" s="63"/>
@@ -5644,12 +5705,17 @@
       <c r="G182" s="61"/>
       <c r="H182" s="63"/>
       <c r="I182" s="63"/>
-      <c r="J182" s="60"/>
-      <c r="K182" s="84"/>
-      <c r="L182" s="84"/>
-      <c r="M182" s="61"/>
-    </row>
-    <row r="183" customHeight="1" spans="2:13">
+      <c r="J182" s="84"/>
+      <c r="K182" s="85"/>
+      <c r="L182" s="85"/>
+      <c r="M182" s="86"/>
+      <c r="O182" s="15"/>
+      <c r="P182" s="16"/>
+      <c r="Q182" s="15"/>
+      <c r="R182" s="16"/>
+      <c r="S182" s="83"/>
+    </row>
+    <row r="183" customHeight="1" spans="2:19">
       <c r="B183" s="15"/>
       <c r="C183" s="16"/>
       <c r="D183" s="63"/>
@@ -5658,12 +5724,17 @@
       <c r="G183" s="61"/>
       <c r="H183" s="63"/>
       <c r="I183" s="63"/>
-      <c r="J183" s="60"/>
-      <c r="K183" s="84"/>
-      <c r="L183" s="84"/>
-      <c r="M183" s="61"/>
-    </row>
-    <row r="184" customHeight="1" spans="2:13">
+      <c r="J183" s="84"/>
+      <c r="K183" s="85"/>
+      <c r="L183" s="85"/>
+      <c r="M183" s="86"/>
+      <c r="O183" s="15"/>
+      <c r="P183" s="16"/>
+      <c r="Q183" s="15"/>
+      <c r="R183" s="16"/>
+      <c r="S183" s="83"/>
+    </row>
+    <row r="184" customHeight="1" spans="2:19">
       <c r="B184" s="15"/>
       <c r="C184" s="16"/>
       <c r="D184" s="63"/>
@@ -5672,12 +5743,17 @@
       <c r="G184" s="61"/>
       <c r="H184" s="63"/>
       <c r="I184" s="63"/>
-      <c r="J184" s="60"/>
-      <c r="K184" s="84"/>
-      <c r="L184" s="84"/>
-      <c r="M184" s="61"/>
-    </row>
-    <row r="185" customHeight="1" spans="2:13">
+      <c r="J184" s="84"/>
+      <c r="K184" s="85"/>
+      <c r="L184" s="85"/>
+      <c r="M184" s="86"/>
+      <c r="O184" s="15"/>
+      <c r="P184" s="16"/>
+      <c r="Q184" s="15"/>
+      <c r="R184" s="16"/>
+      <c r="S184" s="83"/>
+    </row>
+    <row r="185" customHeight="1" spans="2:19">
       <c r="B185" s="15"/>
       <c r="C185" s="16"/>
       <c r="D185" s="63"/>
@@ -5686,12 +5762,17 @@
       <c r="G185" s="61"/>
       <c r="H185" s="63"/>
       <c r="I185" s="63"/>
-      <c r="J185" s="60"/>
-      <c r="K185" s="84"/>
-      <c r="L185" s="84"/>
-      <c r="M185" s="61"/>
-    </row>
-    <row r="186" customHeight="1" spans="2:13">
+      <c r="J185" s="84"/>
+      <c r="K185" s="85"/>
+      <c r="L185" s="85"/>
+      <c r="M185" s="86"/>
+      <c r="O185" s="15"/>
+      <c r="P185" s="16"/>
+      <c r="Q185" s="15"/>
+      <c r="R185" s="16"/>
+      <c r="S185" s="83"/>
+    </row>
+    <row r="186" customHeight="1" spans="2:19">
       <c r="B186" s="15"/>
       <c r="C186" s="16"/>
       <c r="D186" s="63"/>
@@ -5700,12 +5781,17 @@
       <c r="G186" s="61"/>
       <c r="H186" s="63"/>
       <c r="I186" s="63"/>
-      <c r="J186" s="60"/>
-      <c r="K186" s="84"/>
-      <c r="L186" s="84"/>
-      <c r="M186" s="61"/>
-    </row>
-    <row r="187" customHeight="1" spans="2:13">
+      <c r="J186" s="84"/>
+      <c r="K186" s="85"/>
+      <c r="L186" s="85"/>
+      <c r="M186" s="86"/>
+      <c r="O186" s="15"/>
+      <c r="P186" s="16"/>
+      <c r="Q186" s="15"/>
+      <c r="R186" s="16"/>
+      <c r="S186" s="83"/>
+    </row>
+    <row r="187" customHeight="1" spans="2:19">
       <c r="B187" s="15"/>
       <c r="C187" s="16"/>
       <c r="D187" s="63"/>
@@ -5714,12 +5800,17 @@
       <c r="G187" s="61"/>
       <c r="H187" s="63"/>
       <c r="I187" s="63"/>
-      <c r="J187" s="60"/>
-      <c r="K187" s="84"/>
-      <c r="L187" s="84"/>
-      <c r="M187" s="61"/>
-    </row>
-    <row r="188" customHeight="1" spans="2:13">
+      <c r="J187" s="84"/>
+      <c r="K187" s="85"/>
+      <c r="L187" s="85"/>
+      <c r="M187" s="86"/>
+      <c r="O187" s="15"/>
+      <c r="P187" s="16"/>
+      <c r="Q187" s="15"/>
+      <c r="R187" s="16"/>
+      <c r="S187" s="83"/>
+    </row>
+    <row r="188" customHeight="1" spans="2:19">
       <c r="B188" s="15"/>
       <c r="C188" s="16"/>
       <c r="D188" s="63"/>
@@ -5728,12 +5819,17 @@
       <c r="G188" s="61"/>
       <c r="H188" s="63"/>
       <c r="I188" s="63"/>
-      <c r="J188" s="60"/>
-      <c r="K188" s="84"/>
-      <c r="L188" s="84"/>
-      <c r="M188" s="61"/>
-    </row>
-    <row r="189" customHeight="1" spans="2:13">
+      <c r="J188" s="84"/>
+      <c r="K188" s="85"/>
+      <c r="L188" s="85"/>
+      <c r="M188" s="86"/>
+      <c r="O188" s="15"/>
+      <c r="P188" s="16"/>
+      <c r="Q188" s="15"/>
+      <c r="R188" s="16"/>
+      <c r="S188" s="83"/>
+    </row>
+    <row r="189" customHeight="1" spans="2:19">
       <c r="B189" s="15"/>
       <c r="C189" s="16"/>
       <c r="D189" s="63"/>
@@ -5742,12 +5838,17 @@
       <c r="G189" s="61"/>
       <c r="H189" s="63"/>
       <c r="I189" s="63"/>
-      <c r="J189" s="60"/>
-      <c r="K189" s="84"/>
-      <c r="L189" s="84"/>
-      <c r="M189" s="61"/>
-    </row>
-    <row r="190" customHeight="1" spans="2:13">
+      <c r="J189" s="84"/>
+      <c r="K189" s="85"/>
+      <c r="L189" s="85"/>
+      <c r="M189" s="86"/>
+      <c r="O189" s="15"/>
+      <c r="P189" s="16"/>
+      <c r="Q189" s="15"/>
+      <c r="R189" s="16"/>
+      <c r="S189" s="83"/>
+    </row>
+    <row r="190" customHeight="1" spans="2:19">
       <c r="B190" s="15"/>
       <c r="C190" s="16"/>
       <c r="D190" s="63"/>
@@ -5756,12 +5857,17 @@
       <c r="G190" s="61"/>
       <c r="H190" s="63"/>
       <c r="I190" s="63"/>
-      <c r="J190" s="60"/>
-      <c r="K190" s="84"/>
-      <c r="L190" s="84"/>
-      <c r="M190" s="61"/>
-    </row>
-    <row r="191" customHeight="1" spans="2:13">
+      <c r="J190" s="84"/>
+      <c r="K190" s="85"/>
+      <c r="L190" s="85"/>
+      <c r="M190" s="86"/>
+      <c r="O190" s="15"/>
+      <c r="P190" s="16"/>
+      <c r="Q190" s="15"/>
+      <c r="R190" s="16"/>
+      <c r="S190" s="83"/>
+    </row>
+    <row r="191" customHeight="1" spans="2:19">
       <c r="B191" s="15"/>
       <c r="C191" s="16"/>
       <c r="D191" s="63"/>
@@ -5770,12 +5876,17 @@
       <c r="G191" s="61"/>
       <c r="H191" s="63"/>
       <c r="I191" s="63"/>
-      <c r="J191" s="60"/>
-      <c r="K191" s="84"/>
-      <c r="L191" s="84"/>
-      <c r="M191" s="61"/>
-    </row>
-    <row r="192" customHeight="1" spans="2:13">
+      <c r="J191" s="84"/>
+      <c r="K191" s="85"/>
+      <c r="L191" s="85"/>
+      <c r="M191" s="86"/>
+      <c r="O191" s="15"/>
+      <c r="P191" s="16"/>
+      <c r="Q191" s="15"/>
+      <c r="R191" s="16"/>
+      <c r="S191" s="83"/>
+    </row>
+    <row r="192" customHeight="1" spans="2:19">
       <c r="B192" s="15"/>
       <c r="C192" s="16"/>
       <c r="D192" s="63"/>
@@ -5784,10 +5895,15 @@
       <c r="G192" s="61"/>
       <c r="H192" s="63"/>
       <c r="I192" s="63"/>
-      <c r="J192" s="60"/>
-      <c r="K192" s="84"/>
-      <c r="L192" s="84"/>
-      <c r="M192" s="61"/>
+      <c r="J192" s="84"/>
+      <c r="K192" s="85"/>
+      <c r="L192" s="85"/>
+      <c r="M192" s="86"/>
+      <c r="O192" s="15"/>
+      <c r="P192" s="16"/>
+      <c r="Q192" s="15"/>
+      <c r="R192" s="16"/>
+      <c r="S192" s="83"/>
     </row>
     <row r="193" customHeight="1" spans="2:13">
       <c r="B193" s="15"/>
@@ -5798,10 +5914,10 @@
       <c r="G193" s="61"/>
       <c r="H193" s="63"/>
       <c r="I193" s="63"/>
-      <c r="J193" s="60"/>
-      <c r="K193" s="84"/>
-      <c r="L193" s="84"/>
-      <c r="M193" s="61"/>
+      <c r="J193" s="84"/>
+      <c r="K193" s="85"/>
+      <c r="L193" s="85"/>
+      <c r="M193" s="86"/>
     </row>
     <row r="194" customHeight="1" spans="2:13">
       <c r="B194" s="15"/>
@@ -5812,10 +5928,10 @@
       <c r="G194" s="61"/>
       <c r="H194" s="63"/>
       <c r="I194" s="63"/>
-      <c r="J194" s="60"/>
-      <c r="K194" s="84"/>
-      <c r="L194" s="84"/>
-      <c r="M194" s="61"/>
+      <c r="J194" s="84"/>
+      <c r="K194" s="85"/>
+      <c r="L194" s="85"/>
+      <c r="M194" s="86"/>
     </row>
     <row r="195" customHeight="1" spans="2:13">
       <c r="B195" s="15"/>
@@ -5826,10 +5942,10 @@
       <c r="G195" s="61"/>
       <c r="H195" s="63"/>
       <c r="I195" s="63"/>
-      <c r="J195" s="60"/>
-      <c r="K195" s="84"/>
-      <c r="L195" s="84"/>
-      <c r="M195" s="61"/>
+      <c r="J195" s="84"/>
+      <c r="K195" s="85"/>
+      <c r="L195" s="85"/>
+      <c r="M195" s="86"/>
     </row>
     <row r="196" customHeight="1" spans="2:13">
       <c r="B196" s="15"/>
@@ -5840,10 +5956,10 @@
       <c r="G196" s="61"/>
       <c r="H196" s="63"/>
       <c r="I196" s="63"/>
-      <c r="J196" s="60"/>
-      <c r="K196" s="84"/>
-      <c r="L196" s="84"/>
-      <c r="M196" s="61"/>
+      <c r="J196" s="84"/>
+      <c r="K196" s="85"/>
+      <c r="L196" s="85"/>
+      <c r="M196" s="86"/>
     </row>
     <row r="197" customHeight="1" spans="2:13">
       <c r="B197" s="15"/>
@@ -5854,10 +5970,10 @@
       <c r="G197" s="61"/>
       <c r="H197" s="63"/>
       <c r="I197" s="63"/>
-      <c r="J197" s="60"/>
-      <c r="K197" s="84"/>
-      <c r="L197" s="84"/>
-      <c r="M197" s="61"/>
+      <c r="J197" s="84"/>
+      <c r="K197" s="85"/>
+      <c r="L197" s="85"/>
+      <c r="M197" s="86"/>
     </row>
     <row r="198" customHeight="1" spans="2:13">
       <c r="B198" s="15"/>
@@ -5868,10 +5984,10 @@
       <c r="G198" s="61"/>
       <c r="H198" s="63"/>
       <c r="I198" s="63"/>
-      <c r="J198" s="60"/>
-      <c r="K198" s="84"/>
-      <c r="L198" s="84"/>
-      <c r="M198" s="61"/>
+      <c r="J198" s="84"/>
+      <c r="K198" s="85"/>
+      <c r="L198" s="85"/>
+      <c r="M198" s="86"/>
     </row>
     <row r="199" customHeight="1" spans="2:13">
       <c r="B199" s="15"/>
@@ -5882,10 +5998,10 @@
       <c r="G199" s="61"/>
       <c r="H199" s="63"/>
       <c r="I199" s="63"/>
-      <c r="J199" s="60"/>
-      <c r="K199" s="84"/>
-      <c r="L199" s="84"/>
-      <c r="M199" s="61"/>
+      <c r="J199" s="84"/>
+      <c r="K199" s="85"/>
+      <c r="L199" s="85"/>
+      <c r="M199" s="86"/>
     </row>
     <row r="200" customHeight="1" spans="2:13">
       <c r="B200" s="15"/>
@@ -5896,10 +6012,10 @@
       <c r="G200" s="61"/>
       <c r="H200" s="63"/>
       <c r="I200" s="63"/>
-      <c r="J200" s="60"/>
-      <c r="K200" s="84"/>
-      <c r="L200" s="84"/>
-      <c r="M200" s="61"/>
+      <c r="J200" s="84"/>
+      <c r="K200" s="85"/>
+      <c r="L200" s="85"/>
+      <c r="M200" s="86"/>
     </row>
     <row r="201" customHeight="1" spans="2:13">
       <c r="B201" s="15"/>
@@ -5910,10 +6026,10 @@
       <c r="G201" s="61"/>
       <c r="H201" s="63"/>
       <c r="I201" s="63"/>
-      <c r="J201" s="60"/>
-      <c r="K201" s="84"/>
-      <c r="L201" s="84"/>
-      <c r="M201" s="61"/>
+      <c r="J201" s="84"/>
+      <c r="K201" s="85"/>
+      <c r="L201" s="85"/>
+      <c r="M201" s="86"/>
     </row>
     <row r="202" customHeight="1" spans="2:13">
       <c r="B202" s="15"/>
@@ -5924,10 +6040,10 @@
       <c r="G202" s="61"/>
       <c r="H202" s="63"/>
       <c r="I202" s="63"/>
-      <c r="J202" s="60"/>
-      <c r="K202" s="84"/>
-      <c r="L202" s="84"/>
-      <c r="M202" s="61"/>
+      <c r="J202" s="84"/>
+      <c r="K202" s="85"/>
+      <c r="L202" s="85"/>
+      <c r="M202" s="86"/>
     </row>
     <row r="203" customHeight="1" spans="2:13">
       <c r="B203" s="15"/>
@@ -5938,10 +6054,10 @@
       <c r="G203" s="61"/>
       <c r="H203" s="63"/>
       <c r="I203" s="63"/>
-      <c r="J203" s="60"/>
-      <c r="K203" s="84"/>
-      <c r="L203" s="84"/>
-      <c r="M203" s="61"/>
+      <c r="J203" s="84"/>
+      <c r="K203" s="85"/>
+      <c r="L203" s="85"/>
+      <c r="M203" s="86"/>
     </row>
     <row r="204" customHeight="1" spans="2:13">
       <c r="B204" s="15"/>
@@ -5952,10 +6068,10 @@
       <c r="G204" s="61"/>
       <c r="H204" s="63"/>
       <c r="I204" s="63"/>
-      <c r="J204" s="60"/>
-      <c r="K204" s="84"/>
-      <c r="L204" s="84"/>
-      <c r="M204" s="61"/>
+      <c r="J204" s="84"/>
+      <c r="K204" s="85"/>
+      <c r="L204" s="85"/>
+      <c r="M204" s="86"/>
     </row>
     <row r="205" customHeight="1" spans="2:13">
       <c r="B205" s="15"/>
@@ -5966,10 +6082,10 @@
       <c r="G205" s="61"/>
       <c r="H205" s="63"/>
       <c r="I205" s="63"/>
-      <c r="J205" s="60"/>
-      <c r="K205" s="84"/>
-      <c r="L205" s="84"/>
-      <c r="M205" s="61"/>
+      <c r="J205" s="84"/>
+      <c r="K205" s="85"/>
+      <c r="L205" s="85"/>
+      <c r="M205" s="86"/>
     </row>
     <row r="206" customHeight="1" spans="2:13">
       <c r="B206" s="15"/>
@@ -5980,10 +6096,10 @@
       <c r="G206" s="61"/>
       <c r="H206" s="63"/>
       <c r="I206" s="63"/>
-      <c r="J206" s="60"/>
-      <c r="K206" s="84"/>
-      <c r="L206" s="84"/>
-      <c r="M206" s="61"/>
+      <c r="J206" s="84"/>
+      <c r="K206" s="85"/>
+      <c r="L206" s="85"/>
+      <c r="M206" s="86"/>
     </row>
     <row r="207" customHeight="1" spans="2:13">
       <c r="B207" s="15"/>
@@ -5994,10 +6110,10 @@
       <c r="G207" s="61"/>
       <c r="H207" s="63"/>
       <c r="I207" s="63"/>
-      <c r="J207" s="60"/>
-      <c r="K207" s="84"/>
-      <c r="L207" s="84"/>
-      <c r="M207" s="61"/>
+      <c r="J207" s="84"/>
+      <c r="K207" s="85"/>
+      <c r="L207" s="85"/>
+      <c r="M207" s="86"/>
     </row>
     <row r="208" customHeight="1" spans="2:13">
       <c r="B208" s="15"/>
@@ -6008,10 +6124,10 @@
       <c r="G208" s="61"/>
       <c r="H208" s="63"/>
       <c r="I208" s="63"/>
-      <c r="J208" s="60"/>
-      <c r="K208" s="84"/>
-      <c r="L208" s="84"/>
-      <c r="M208" s="61"/>
+      <c r="J208" s="84"/>
+      <c r="K208" s="85"/>
+      <c r="L208" s="85"/>
+      <c r="M208" s="86"/>
     </row>
     <row r="209" customHeight="1" spans="2:13">
       <c r="B209" s="15"/>
@@ -6022,80 +6138,34 @@
       <c r="G209" s="61"/>
       <c r="H209" s="63"/>
       <c r="I209" s="63"/>
-      <c r="J209" s="60"/>
-      <c r="K209" s="84"/>
-      <c r="L209" s="84"/>
-      <c r="M209" s="61"/>
-    </row>
-    <row r="210">
-      <c r="O210" t="inlineStr">
-        <is>
-          <t>图纸（专业槽位）</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="O211"/>
-    </row>
-    <row r="212">
-      <c r="O212"/>
-    </row>
-    <row r="213">
-      <c r="O213"/>
-    </row>
-    <row r="214">
-      <c r="O214"/>
-    </row>
-    <row r="215">
-      <c r="O215"/>
-    </row>
-    <row r="216">
-      <c r="O216"/>
-    </row>
-    <row r="217">
-      <c r="O217"/>
-    </row>
-    <row r="218">
-      <c r="O218"/>
-    </row>
-    <row r="219">
-      <c r="O219"/>
-    </row>
-    <row r="220">
-      <c r="O220"/>
-    </row>
-    <row r="221">
-      <c r="O221"/>
-    </row>
-    <row r="222">
-      <c r="O222"/>
-    </row>
-    <row r="223">
-      <c r="O223"/>
-    </row>
-    <row r="224">
-      <c r="O224"/>
-    </row>
-    <row r="225">
-      <c r="O225"/>
-    </row>
-    <row r="226">
-      <c r="O226"/>
-    </row>
-    <row r="227">
-      <c r="O227"/>
-    </row>
-    <row r="228">
-      <c r="O228"/>
-    </row>
-    <row r="229">
-      <c r="O229"/>
-    </row>
-    <row r="230">
-      <c r="O230"/>
-    </row>
+      <c r="J209" s="84"/>
+      <c r="K209" s="85"/>
+      <c r="L209" s="85"/>
+      <c r="M209" s="86"/>
+    </row>
+    <row r="210" ht="13.5"/>
+    <row r="211" ht="13.5"/>
+    <row r="212" ht="13.5"/>
+    <row r="213" ht="13.5"/>
+    <row r="214" ht="13.5"/>
+    <row r="215" ht="13.5"/>
+    <row r="216" ht="13.5"/>
+    <row r="217" ht="13.5"/>
+    <row r="218" ht="13.5"/>
+    <row r="219" ht="13.5"/>
+    <row r="220" ht="13.5"/>
+    <row r="221" ht="13.5"/>
+    <row r="222" ht="13.5"/>
+    <row r="223" ht="13.5"/>
+    <row r="224" ht="13.5"/>
+    <row r="225" ht="13.5"/>
+    <row r="226" ht="13.5"/>
+    <row r="227" ht="13.5"/>
+    <row r="228" ht="13.5"/>
+    <row r="229" ht="13.5"/>
+    <row r="230" ht="13.5"/>
   </sheetData>
-  <mergeCells count="588">
+  <mergeCells count="711">
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="K2:N2"/>
@@ -6365,147 +6435,187 @@
     <mergeCell ref="Q122:R122"/>
     <mergeCell ref="B123:C123"/>
     <mergeCell ref="F123:G123"/>
+    <mergeCell ref="J123:M123"/>
     <mergeCell ref="O123:P123"/>
     <mergeCell ref="Q123:R123"/>
     <mergeCell ref="B124:C124"/>
     <mergeCell ref="F124:G124"/>
+    <mergeCell ref="J124:M124"/>
     <mergeCell ref="O124:P124"/>
     <mergeCell ref="Q124:R124"/>
     <mergeCell ref="B125:C125"/>
     <mergeCell ref="F125:G125"/>
+    <mergeCell ref="J125:M125"/>
     <mergeCell ref="O125:P125"/>
     <mergeCell ref="Q125:R125"/>
     <mergeCell ref="B126:C126"/>
     <mergeCell ref="F126:G126"/>
+    <mergeCell ref="J126:M126"/>
     <mergeCell ref="O126:P126"/>
     <mergeCell ref="Q126:R126"/>
     <mergeCell ref="B127:C127"/>
     <mergeCell ref="F127:G127"/>
+    <mergeCell ref="J127:M127"/>
     <mergeCell ref="B128:C128"/>
     <mergeCell ref="F128:G128"/>
+    <mergeCell ref="J128:M128"/>
     <mergeCell ref="O128:S128"/>
     <mergeCell ref="B129:C129"/>
     <mergeCell ref="F129:G129"/>
+    <mergeCell ref="J129:M129"/>
     <mergeCell ref="O129:P129"/>
     <mergeCell ref="Q129:R129"/>
     <mergeCell ref="B130:C130"/>
     <mergeCell ref="F130:G130"/>
+    <mergeCell ref="J130:M130"/>
     <mergeCell ref="O130:P130"/>
     <mergeCell ref="Q130:R130"/>
     <mergeCell ref="B131:C131"/>
     <mergeCell ref="F131:G131"/>
+    <mergeCell ref="J131:M131"/>
     <mergeCell ref="O131:P131"/>
     <mergeCell ref="Q131:R131"/>
     <mergeCell ref="B132:C132"/>
     <mergeCell ref="F132:G132"/>
+    <mergeCell ref="J132:M132"/>
     <mergeCell ref="O132:P132"/>
     <mergeCell ref="Q132:R132"/>
     <mergeCell ref="B133:C133"/>
     <mergeCell ref="F133:G133"/>
+    <mergeCell ref="J133:M133"/>
     <mergeCell ref="O133:P133"/>
     <mergeCell ref="Q133:R133"/>
     <mergeCell ref="B134:C134"/>
     <mergeCell ref="F134:G134"/>
+    <mergeCell ref="J134:M134"/>
     <mergeCell ref="B135:C135"/>
     <mergeCell ref="F135:G135"/>
+    <mergeCell ref="J135:M135"/>
     <mergeCell ref="O135:S135"/>
     <mergeCell ref="B136:C136"/>
     <mergeCell ref="F136:G136"/>
+    <mergeCell ref="J136:M136"/>
     <mergeCell ref="O136:P136"/>
     <mergeCell ref="Q136:R136"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="F137:G137"/>
+    <mergeCell ref="J137:M137"/>
     <mergeCell ref="O137:P137"/>
     <mergeCell ref="Q137:R137"/>
     <mergeCell ref="B138:C138"/>
     <mergeCell ref="F138:G138"/>
+    <mergeCell ref="J138:M138"/>
     <mergeCell ref="O138:P138"/>
     <mergeCell ref="Q138:R138"/>
     <mergeCell ref="B139:C139"/>
     <mergeCell ref="F139:G139"/>
+    <mergeCell ref="J139:M139"/>
     <mergeCell ref="O139:P139"/>
     <mergeCell ref="Q139:R139"/>
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="F140:G140"/>
+    <mergeCell ref="J140:M140"/>
     <mergeCell ref="O140:P140"/>
     <mergeCell ref="Q140:R140"/>
     <mergeCell ref="B141:C141"/>
     <mergeCell ref="F141:G141"/>
+    <mergeCell ref="J141:M141"/>
     <mergeCell ref="B142:C142"/>
     <mergeCell ref="F142:G142"/>
+    <mergeCell ref="J142:M142"/>
     <mergeCell ref="O142:S142"/>
     <mergeCell ref="B143:C143"/>
     <mergeCell ref="F143:G143"/>
+    <mergeCell ref="J143:M143"/>
     <mergeCell ref="O143:P143"/>
     <mergeCell ref="Q143:R143"/>
     <mergeCell ref="B144:C144"/>
     <mergeCell ref="F144:G144"/>
+    <mergeCell ref="J144:M144"/>
     <mergeCell ref="O144:P144"/>
     <mergeCell ref="Q144:R144"/>
     <mergeCell ref="B145:C145"/>
     <mergeCell ref="F145:G145"/>
+    <mergeCell ref="J145:M145"/>
     <mergeCell ref="O145:P145"/>
     <mergeCell ref="Q145:R145"/>
     <mergeCell ref="B146:C146"/>
     <mergeCell ref="F146:G146"/>
+    <mergeCell ref="J146:M146"/>
     <mergeCell ref="O146:P146"/>
     <mergeCell ref="Q146:R146"/>
     <mergeCell ref="B147:C147"/>
     <mergeCell ref="F147:G147"/>
+    <mergeCell ref="J147:M147"/>
     <mergeCell ref="O147:P147"/>
     <mergeCell ref="Q147:R147"/>
     <mergeCell ref="B148:C148"/>
     <mergeCell ref="F148:G148"/>
+    <mergeCell ref="J148:M148"/>
     <mergeCell ref="B149:C149"/>
     <mergeCell ref="F149:G149"/>
+    <mergeCell ref="J149:M149"/>
     <mergeCell ref="O149:S149"/>
     <mergeCell ref="B150:C150"/>
     <mergeCell ref="F150:G150"/>
+    <mergeCell ref="J150:M150"/>
     <mergeCell ref="O150:P150"/>
     <mergeCell ref="Q150:R150"/>
     <mergeCell ref="B151:C151"/>
     <mergeCell ref="F151:G151"/>
+    <mergeCell ref="J151:M151"/>
     <mergeCell ref="O151:P151"/>
     <mergeCell ref="Q151:R151"/>
     <mergeCell ref="B152:C152"/>
     <mergeCell ref="F152:G152"/>
+    <mergeCell ref="J152:M152"/>
     <mergeCell ref="O152:P152"/>
     <mergeCell ref="Q152:R152"/>
     <mergeCell ref="B153:C153"/>
     <mergeCell ref="F153:G153"/>
+    <mergeCell ref="J153:M153"/>
     <mergeCell ref="O153:P153"/>
     <mergeCell ref="Q153:R153"/>
     <mergeCell ref="B154:C154"/>
     <mergeCell ref="F154:G154"/>
+    <mergeCell ref="J154:M154"/>
     <mergeCell ref="O154:P154"/>
     <mergeCell ref="Q154:R154"/>
     <mergeCell ref="B155:C155"/>
     <mergeCell ref="F155:G155"/>
+    <mergeCell ref="J155:M155"/>
     <mergeCell ref="B156:C156"/>
     <mergeCell ref="F156:G156"/>
+    <mergeCell ref="J156:M156"/>
     <mergeCell ref="O156:S156"/>
     <mergeCell ref="B157:C157"/>
     <mergeCell ref="F157:G157"/>
+    <mergeCell ref="J157:M157"/>
     <mergeCell ref="O157:P157"/>
     <mergeCell ref="Q157:R157"/>
     <mergeCell ref="B158:C158"/>
     <mergeCell ref="F158:G158"/>
+    <mergeCell ref="J158:M158"/>
     <mergeCell ref="O158:P158"/>
     <mergeCell ref="Q158:R158"/>
     <mergeCell ref="B159:C159"/>
     <mergeCell ref="F159:G159"/>
+    <mergeCell ref="J159:M159"/>
     <mergeCell ref="O159:P159"/>
     <mergeCell ref="Q159:R159"/>
     <mergeCell ref="B160:C160"/>
     <mergeCell ref="F160:G160"/>
+    <mergeCell ref="J160:M160"/>
     <mergeCell ref="O160:P160"/>
     <mergeCell ref="Q160:R160"/>
     <mergeCell ref="B161:C161"/>
     <mergeCell ref="F161:G161"/>
+    <mergeCell ref="J161:M161"/>
     <mergeCell ref="O161:P161"/>
     <mergeCell ref="Q161:R161"/>
     <mergeCell ref="B162:C162"/>
     <mergeCell ref="F162:G162"/>
+    <mergeCell ref="J162:M162"/>
     <mergeCell ref="O163:S163"/>
     <mergeCell ref="O164:P164"/>
     <mergeCell ref="Q164:R164"/>
@@ -6521,90 +6631,173 @@
     <mergeCell ref="Q167:R167"/>
     <mergeCell ref="B168:C168"/>
     <mergeCell ref="F168:G168"/>
+    <mergeCell ref="J168:M168"/>
     <mergeCell ref="O168:P168"/>
     <mergeCell ref="Q168:R168"/>
     <mergeCell ref="B169:C169"/>
     <mergeCell ref="F169:G169"/>
+    <mergeCell ref="J169:M169"/>
     <mergeCell ref="B170:C170"/>
     <mergeCell ref="F170:G170"/>
+    <mergeCell ref="J170:M170"/>
     <mergeCell ref="B171:C171"/>
     <mergeCell ref="F171:G171"/>
+    <mergeCell ref="J171:M171"/>
     <mergeCell ref="B172:C172"/>
     <mergeCell ref="F172:G172"/>
+    <mergeCell ref="J172:M172"/>
+    <mergeCell ref="O172:S172"/>
     <mergeCell ref="B173:C173"/>
     <mergeCell ref="F173:G173"/>
+    <mergeCell ref="J173:M173"/>
+    <mergeCell ref="O173:P173"/>
+    <mergeCell ref="Q173:R173"/>
     <mergeCell ref="B174:C174"/>
     <mergeCell ref="F174:G174"/>
+    <mergeCell ref="J174:M174"/>
+    <mergeCell ref="O174:P174"/>
+    <mergeCell ref="Q174:R174"/>
     <mergeCell ref="B175:C175"/>
     <mergeCell ref="F175:G175"/>
+    <mergeCell ref="J175:M175"/>
+    <mergeCell ref="O175:P175"/>
+    <mergeCell ref="Q175:R175"/>
     <mergeCell ref="B176:C176"/>
     <mergeCell ref="F176:G176"/>
+    <mergeCell ref="J176:M176"/>
+    <mergeCell ref="O176:P176"/>
+    <mergeCell ref="Q176:R176"/>
     <mergeCell ref="B177:C177"/>
     <mergeCell ref="F177:G177"/>
+    <mergeCell ref="J177:M177"/>
+    <mergeCell ref="O177:P177"/>
+    <mergeCell ref="Q177:R177"/>
     <mergeCell ref="B178:C178"/>
     <mergeCell ref="F178:G178"/>
+    <mergeCell ref="J178:M178"/>
+    <mergeCell ref="O178:P178"/>
+    <mergeCell ref="Q178:R178"/>
     <mergeCell ref="B179:C179"/>
     <mergeCell ref="F179:G179"/>
+    <mergeCell ref="J179:M179"/>
+    <mergeCell ref="O179:P179"/>
+    <mergeCell ref="Q179:R179"/>
     <mergeCell ref="B180:C180"/>
     <mergeCell ref="F180:G180"/>
+    <mergeCell ref="J180:M180"/>
+    <mergeCell ref="O180:P180"/>
+    <mergeCell ref="Q180:R180"/>
     <mergeCell ref="B181:C181"/>
     <mergeCell ref="F181:G181"/>
+    <mergeCell ref="J181:M181"/>
+    <mergeCell ref="O181:P181"/>
+    <mergeCell ref="Q181:R181"/>
     <mergeCell ref="B182:C182"/>
     <mergeCell ref="F182:G182"/>
+    <mergeCell ref="J182:M182"/>
+    <mergeCell ref="O182:P182"/>
+    <mergeCell ref="Q182:R182"/>
     <mergeCell ref="B183:C183"/>
     <mergeCell ref="F183:G183"/>
+    <mergeCell ref="J183:M183"/>
+    <mergeCell ref="O183:P183"/>
+    <mergeCell ref="Q183:R183"/>
     <mergeCell ref="B184:C184"/>
     <mergeCell ref="F184:G184"/>
+    <mergeCell ref="J184:M184"/>
+    <mergeCell ref="O184:P184"/>
+    <mergeCell ref="Q184:R184"/>
     <mergeCell ref="B185:C185"/>
     <mergeCell ref="F185:G185"/>
+    <mergeCell ref="J185:M185"/>
+    <mergeCell ref="O185:P185"/>
+    <mergeCell ref="Q185:R185"/>
     <mergeCell ref="B186:C186"/>
     <mergeCell ref="F186:G186"/>
+    <mergeCell ref="J186:M186"/>
+    <mergeCell ref="O186:P186"/>
+    <mergeCell ref="Q186:R186"/>
     <mergeCell ref="B187:C187"/>
     <mergeCell ref="F187:G187"/>
+    <mergeCell ref="J187:M187"/>
+    <mergeCell ref="O187:P187"/>
+    <mergeCell ref="Q187:R187"/>
     <mergeCell ref="B188:C188"/>
     <mergeCell ref="F188:G188"/>
+    <mergeCell ref="J188:M188"/>
+    <mergeCell ref="O188:P188"/>
+    <mergeCell ref="Q188:R188"/>
     <mergeCell ref="B189:C189"/>
     <mergeCell ref="F189:G189"/>
+    <mergeCell ref="J189:M189"/>
+    <mergeCell ref="O189:P189"/>
+    <mergeCell ref="Q189:R189"/>
     <mergeCell ref="B190:C190"/>
     <mergeCell ref="F190:G190"/>
+    <mergeCell ref="J190:M190"/>
+    <mergeCell ref="O190:P190"/>
+    <mergeCell ref="Q190:R190"/>
     <mergeCell ref="B191:C191"/>
     <mergeCell ref="F191:G191"/>
+    <mergeCell ref="J191:M191"/>
+    <mergeCell ref="O191:P191"/>
+    <mergeCell ref="Q191:R191"/>
     <mergeCell ref="B192:C192"/>
     <mergeCell ref="F192:G192"/>
+    <mergeCell ref="J192:M192"/>
+    <mergeCell ref="O192:P192"/>
+    <mergeCell ref="Q192:R192"/>
     <mergeCell ref="B193:C193"/>
     <mergeCell ref="F193:G193"/>
+    <mergeCell ref="J193:M193"/>
     <mergeCell ref="B194:C194"/>
     <mergeCell ref="F194:G194"/>
+    <mergeCell ref="J194:M194"/>
     <mergeCell ref="B195:C195"/>
     <mergeCell ref="F195:G195"/>
+    <mergeCell ref="J195:M195"/>
     <mergeCell ref="B196:C196"/>
     <mergeCell ref="F196:G196"/>
+    <mergeCell ref="J196:M196"/>
     <mergeCell ref="B197:C197"/>
     <mergeCell ref="F197:G197"/>
+    <mergeCell ref="J197:M197"/>
     <mergeCell ref="B198:C198"/>
     <mergeCell ref="F198:G198"/>
+    <mergeCell ref="J198:M198"/>
     <mergeCell ref="B199:C199"/>
     <mergeCell ref="F199:G199"/>
+    <mergeCell ref="J199:M199"/>
     <mergeCell ref="B200:C200"/>
     <mergeCell ref="F200:G200"/>
+    <mergeCell ref="J200:M200"/>
     <mergeCell ref="B201:C201"/>
     <mergeCell ref="F201:G201"/>
+    <mergeCell ref="J201:M201"/>
     <mergeCell ref="B202:C202"/>
     <mergeCell ref="F202:G202"/>
+    <mergeCell ref="J202:M202"/>
     <mergeCell ref="B203:C203"/>
     <mergeCell ref="F203:G203"/>
+    <mergeCell ref="J203:M203"/>
     <mergeCell ref="B204:C204"/>
     <mergeCell ref="F204:G204"/>
+    <mergeCell ref="J204:M204"/>
     <mergeCell ref="B205:C205"/>
     <mergeCell ref="F205:G205"/>
+    <mergeCell ref="J205:M205"/>
     <mergeCell ref="B206:C206"/>
     <mergeCell ref="F206:G206"/>
+    <mergeCell ref="J206:M206"/>
     <mergeCell ref="B207:C207"/>
     <mergeCell ref="F207:G207"/>
+    <mergeCell ref="J207:M207"/>
     <mergeCell ref="B208:C208"/>
     <mergeCell ref="F208:G208"/>
+    <mergeCell ref="J208:M208"/>
     <mergeCell ref="B209:C209"/>
     <mergeCell ref="F209:G209"/>
+    <mergeCell ref="J209:M209"/>
     <mergeCell ref="B36:B43"/>
     <mergeCell ref="B46:B54"/>
     <mergeCell ref="B57:B59"/>
